--- a/FIFA.xlsx
+++ b/FIFA.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muhammad Faisal\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analytics-portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF43D4D-A019-499A-A05B-09651743E3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E730D9-4524-4C8C-9DF6-90B663A03DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" xr2:uid="{BB1EA6DA-86EB-4FC3-997E-079B42B60F51}"/>
   </bookViews>
   <sheets>
-    <sheet name="GROUP1" sheetId="2" r:id="rId1"/>
+    <sheet name="GROUP 1" sheetId="2" r:id="rId1"/>
     <sheet name="FIFA-2026 G1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -377,7 +377,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -402,13 +402,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -418,6 +411,22 @@
     <font>
       <b/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -471,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -482,15 +491,34 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1365,1701 +1393,1703 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E23B7C48-8229-4FB4-8B7A-ED153A6D01FB}">
   <dimension ref="A1:G75"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="31.8" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.77734375" customWidth="1"/>
-    <col min="2" max="2" width="19.44140625" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="19.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21" style="7" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" style="13" customWidth="1"/>
+    <col min="5" max="5" width="23.21875" style="10" customWidth="1"/>
+    <col min="6" max="7" width="19.44140625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A2" s="7">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="4">
-        <v>2</v>
-      </c>
-      <c r="G2" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="F2" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="6">
+        <v>2</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="4">
-        <v>2</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="F3" s="6">
+        <v>2</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="4">
-        <v>1</v>
-      </c>
-      <c r="G4" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A5" s="7">
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="6">
         <v>4</v>
       </c>
-      <c r="G5" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A6" s="7">
+      <c r="G5" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="4">
-        <v>1</v>
-      </c>
-      <c r="G6" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A7" s="7">
+      <c r="F6" s="6">
+        <v>1</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="4">
-        <v>1</v>
-      </c>
-      <c r="G7" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A8" s="7">
+      <c r="F7" s="6">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4">
-        <v>1</v>
-      </c>
-      <c r="G8" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A9" s="7">
+      <c r="F8" s="6">
+        <v>1</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="4">
-        <v>2</v>
-      </c>
-      <c r="G9" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A10" s="7">
+      <c r="F9" s="6">
+        <v>2</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="6">
         <v>7</v>
       </c>
-      <c r="G10" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A11" s="7">
+      <c r="G10" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="4">
-        <v>1</v>
-      </c>
-      <c r="G11" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A12" s="7">
+      <c r="F11" s="6">
+        <v>1</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="4">
-        <v>2</v>
-      </c>
-      <c r="G12" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A13" s="7">
+      <c r="F12" s="6">
+        <v>2</v>
+      </c>
+      <c r="G12" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="6">
         <v>5</v>
       </c>
-      <c r="G13" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A14" s="7">
+      <c r="G13" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="4">
-        <v>1</v>
-      </c>
-      <c r="G14" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A15" s="7">
+      <c r="F14" s="6">
+        <v>1</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F15" s="4">
-        <v>2</v>
-      </c>
-      <c r="G15" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A16" s="7">
+      <c r="F15" s="6">
+        <v>2</v>
+      </c>
+      <c r="G15" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="4">
-        <v>0</v>
-      </c>
-      <c r="G16" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A17" s="7">
+      <c r="F16" s="6">
+        <v>0</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A18" s="7">
+      <c r="F17" s="6">
+        <v>1</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="4">
-        <v>3</v>
-      </c>
-      <c r="G18" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A19" s="7">
+      <c r="F18" s="6">
+        <v>3</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="6">
         <v>4</v>
       </c>
-      <c r="G19" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A20" s="7">
+      <c r="G19" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="4">
-        <v>3</v>
-      </c>
-      <c r="G20" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A21" s="7">
+      <c r="F20" s="6">
+        <v>3</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F21" s="4">
-        <v>3</v>
-      </c>
-      <c r="G21" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A22" s="7">
+      <c r="F21" s="6">
+        <v>3</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="6">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A23" s="7">
+      <c r="F22" s="6">
+        <v>1</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="4">
-        <v>3</v>
-      </c>
-      <c r="G23" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A24" s="7">
+      <c r="F23" s="6">
+        <v>3</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="6">
         <v>4</v>
       </c>
-      <c r="G24" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A25" s="7">
+      <c r="G24" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F25" s="4">
-        <v>1</v>
-      </c>
-      <c r="G25" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A26" s="7">
+      <c r="F25" s="6">
+        <v>1</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="6">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F26" s="4">
-        <v>1</v>
-      </c>
-      <c r="G26" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A27" s="7">
+      <c r="F26" s="6">
+        <v>1</v>
+      </c>
+      <c r="G26" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="6">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A28" s="7">
+      <c r="F27" s="6">
+        <v>1</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="6">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="4">
+      <c r="F28" s="6">
         <v>4</v>
       </c>
-      <c r="G28" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A29" s="7">
+      <c r="G28" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="6">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="6">
         <v>6</v>
       </c>
-      <c r="G29" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A30" s="7">
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="6">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="4">
-        <v>0</v>
-      </c>
-      <c r="G30" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A31" s="7">
+      <c r="F30" s="6">
+        <v>0</v>
+      </c>
+      <c r="G30" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="6">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F31" s="4">
-        <v>3</v>
-      </c>
-      <c r="G31" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A32" s="7">
+      <c r="F31" s="6">
+        <v>3</v>
+      </c>
+      <c r="G31" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="6">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F32" s="4">
-        <v>2</v>
-      </c>
-      <c r="G32" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A33" s="7">
+      <c r="F32" s="6">
+        <v>2</v>
+      </c>
+      <c r="G32" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="6">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="F33" s="4">
-        <v>0</v>
-      </c>
-      <c r="G33" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A34" s="7">
+      <c r="F33" s="6">
+        <v>0</v>
+      </c>
+      <c r="G33" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="6">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="4" t="s">
+      <c r="C34" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F34" s="4">
-        <v>2</v>
-      </c>
-      <c r="G34" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A35" s="7">
+      <c r="F34" s="6">
+        <v>2</v>
+      </c>
+      <c r="G34" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="F35" s="4">
-        <v>0</v>
-      </c>
-      <c r="G35" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A36" s="7">
+      <c r="F35" s="6">
+        <v>0</v>
+      </c>
+      <c r="G35" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="4" t="s">
+      <c r="C36" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="6">
         <v>5</v>
       </c>
-      <c r="G36" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A37" s="7">
+      <c r="G36" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="6">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="4" t="s">
+      <c r="C37" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="6">
         <v>4</v>
       </c>
-      <c r="G37" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A38" s="7">
+      <c r="G37" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="6">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="4" t="s">
+      <c r="C38" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F38" s="4">
-        <v>0</v>
-      </c>
-      <c r="G38" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A39" s="7">
+      <c r="F38" s="6">
+        <v>0</v>
+      </c>
+      <c r="G38" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="6">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="4" t="s">
+      <c r="E39" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F39" s="4">
-        <v>3</v>
-      </c>
-      <c r="G39" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A40" s="7">
+      <c r="F39" s="6">
+        <v>3</v>
+      </c>
+      <c r="G39" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A40" s="6">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="6">
         <v>4</v>
       </c>
-      <c r="G40" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A41" s="7">
+      <c r="G40" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A41" s="6">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="C41" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F41" s="4">
-        <v>2</v>
-      </c>
-      <c r="G41" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A42" s="7">
+      <c r="F41" s="6">
+        <v>2</v>
+      </c>
+      <c r="G41" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A42" s="6">
         <v>41</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F42" s="4">
-        <v>3</v>
-      </c>
-      <c r="G42" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A43" s="7">
+      <c r="F42" s="6">
+        <v>3</v>
+      </c>
+      <c r="G42" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="6">
         <v>42</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="C43" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F43" s="4">
-        <v>3</v>
-      </c>
-      <c r="G43" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A44" s="7">
+      <c r="F43" s="6">
+        <v>3</v>
+      </c>
+      <c r="G43" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="6">
         <v>43</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C44" s="4" t="s">
+      <c r="C44" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F44" s="4">
-        <v>2</v>
-      </c>
-      <c r="G44" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A45" s="7">
+      <c r="F44" s="6">
+        <v>2</v>
+      </c>
+      <c r="G44" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="6">
         <v>44</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="C45" s="4" t="s">
+      <c r="C45" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F45" s="4">
-        <v>1</v>
-      </c>
-      <c r="G45" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A46" s="7">
+      <c r="F45" s="6">
+        <v>1</v>
+      </c>
+      <c r="G45" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="6">
         <v>45</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F46" s="4">
+      <c r="F46" s="6">
         <v>5</v>
       </c>
-      <c r="G46" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A47" s="7">
+      <c r="G46" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A47" s="6">
         <v>46</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="F47" s="4">
-        <v>1</v>
-      </c>
-      <c r="G47" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A48" s="7">
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A48" s="6">
         <v>47</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C48" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F48" s="4">
-        <v>0</v>
-      </c>
-      <c r="G48" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A49" s="7">
+      <c r="F48" s="6">
+        <v>0</v>
+      </c>
+      <c r="G48" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A49" s="6">
         <v>48</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C49" s="4" t="s">
+      <c r="C49" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="F49" s="4">
-        <v>0</v>
-      </c>
-      <c r="G49" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A50" s="7">
+      <c r="F49" s="6">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="6">
         <v>49</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C50" s="4" t="s">
+      <c r="C50" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="F50" s="4">
-        <v>3</v>
-      </c>
-      <c r="G50" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A51" s="7">
+      <c r="F50" s="6">
+        <v>3</v>
+      </c>
+      <c r="G50" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="6">
         <v>50</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C51" s="4" t="s">
+      <c r="C51" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="F51" s="4">
-        <v>1</v>
-      </c>
-      <c r="G51" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A52" s="7">
+      <c r="F51" s="6">
+        <v>1</v>
+      </c>
+      <c r="G51" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="6">
         <v>51</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C52" s="4" t="s">
+      <c r="C52" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="F52" s="4">
-        <v>2</v>
-      </c>
-      <c r="G52" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A53" s="7">
+      <c r="F52" s="6">
+        <v>2</v>
+      </c>
+      <c r="G52" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="6">
         <v>52</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C53" s="4" t="s">
+      <c r="C53" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="F53" s="4">
-        <v>3</v>
-      </c>
-      <c r="G53" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A54" s="7">
+      <c r="F53" s="6">
+        <v>3</v>
+      </c>
+      <c r="G53" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="6">
         <v>53</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C54" s="4" t="s">
+      <c r="C54" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="F54" s="4">
-        <v>0</v>
-      </c>
-      <c r="G54" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A55" s="7">
+      <c r="F54" s="6">
+        <v>0</v>
+      </c>
+      <c r="G54" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="6">
         <v>54</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C55" s="4" t="s">
+      <c r="C55" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="F55" s="4">
+      <c r="F55" s="6">
         <v>4</v>
       </c>
-      <c r="G55" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A56" s="7">
+      <c r="G55" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="6">
         <v>55</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C56" s="4" t="s">
+      <c r="C56" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="F56" s="4">
-        <v>3</v>
-      </c>
-      <c r="G56" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A57" s="7">
+      <c r="F56" s="6">
+        <v>3</v>
+      </c>
+      <c r="G56" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="6">
         <v>56</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C57" s="4" t="s">
+      <c r="C57" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F57" s="4">
-        <v>0</v>
-      </c>
-      <c r="G57" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A58" s="7">
+      <c r="F57" s="6">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="6">
         <v>57</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C58" s="4" t="s">
+      <c r="C58" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="F58" s="4">
-        <v>0</v>
-      </c>
-      <c r="G58" s="4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A59" s="7">
+      <c r="F58" s="6">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="6">
         <v>58</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C59" s="4" t="s">
+      <c r="C59" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="F59" s="4">
-        <v>2</v>
-      </c>
-      <c r="G59" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A60" s="7">
+      <c r="F59" s="6">
+        <v>2</v>
+      </c>
+      <c r="G59" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="6">
         <v>59</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C60" s="4" t="s">
+      <c r="C60" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F60" s="4">
-        <v>1</v>
-      </c>
-      <c r="G60" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A61" s="7">
+      <c r="F60" s="6">
+        <v>1</v>
+      </c>
+      <c r="G60" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="6">
         <v>60</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C61" s="4" t="s">
+      <c r="C61" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="F61" s="4">
-        <v>3</v>
-      </c>
-      <c r="G61" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A62" s="7">
+      <c r="F61" s="6">
+        <v>3</v>
+      </c>
+      <c r="G61" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="6">
         <v>61</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C62" s="4" t="s">
+      <c r="C62" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="F62" s="4">
-        <v>1</v>
-      </c>
-      <c r="G62" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A63" s="7">
+      <c r="F62" s="6">
+        <v>1</v>
+      </c>
+      <c r="G62" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="6">
         <v>62</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C63" s="4" t="s">
+      <c r="C63" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="F63" s="4">
+      <c r="F63" s="6">
         <v>5</v>
       </c>
-      <c r="G63" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A64" s="7">
+      <c r="G63" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A64" s="6">
         <v>63</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C64" s="4" t="s">
+      <c r="C64" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F64" s="4">
-        <v>0</v>
-      </c>
-      <c r="G64" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A65" s="7">
+      <c r="F64" s="6">
+        <v>0</v>
+      </c>
+      <c r="G64" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A65" s="6">
         <v>64</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C65" s="4" t="s">
+      <c r="C65" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="F65" s="4">
-        <v>1</v>
-      </c>
-      <c r="G65" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A66" s="7">
+      <c r="F65" s="6">
+        <v>1</v>
+      </c>
+      <c r="G65" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A66" s="6">
         <v>65</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="C66" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="F66" s="4">
-        <v>1</v>
-      </c>
-      <c r="G66" s="4">
+      <c r="F66" s="6">
+        <v>1</v>
+      </c>
+      <c r="G66" s="6">
         <v>4</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A67" s="7">
+    <row r="67" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A67" s="6">
         <v>66</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="C67" s="4" t="s">
+      <c r="C67" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="F67" s="4">
+      <c r="F67" s="6">
         <v>5</v>
       </c>
-      <c r="G67" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A68" s="7">
+      <c r="G67" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A68" s="6">
         <v>67</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C68" s="4" t="s">
+      <c r="C68" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="F68" s="4">
-        <v>3</v>
-      </c>
-      <c r="G68" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A69" s="7">
+      <c r="F68" s="6">
+        <v>3</v>
+      </c>
+      <c r="G68" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A69" s="6">
         <v>68</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C69" s="4" t="s">
+      <c r="C69" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="F69" s="4">
-        <v>3</v>
-      </c>
-      <c r="G69" s="4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A70" s="7">
+      <c r="F69" s="6">
+        <v>3</v>
+      </c>
+      <c r="G69" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A70" s="6">
         <v>69</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="F70" s="4">
-        <v>0</v>
-      </c>
-      <c r="G70" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A71" s="7">
+      <c r="F70" s="6">
+        <v>0</v>
+      </c>
+      <c r="G70" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A71" s="6">
         <v>70</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C71" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="F71" s="4">
-        <v>3</v>
-      </c>
-      <c r="G71" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A72" s="7">
+      <c r="F71" s="6">
+        <v>3</v>
+      </c>
+      <c r="G71" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A72" s="6">
         <v>71</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C72" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="F72" s="4">
-        <v>2</v>
-      </c>
-      <c r="G72" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A73" s="7">
+      <c r="F72" s="6">
+        <v>2</v>
+      </c>
+      <c r="G72" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A73" s="6">
         <v>72</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="C73" s="4" t="s">
+      <c r="C73" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="F73" s="4">
-        <v>2</v>
-      </c>
-      <c r="G73" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="25.8" x14ac:dyDescent="0.3">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="5"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
-      <c r="G75" s="5"/>
+      <c r="F73" s="6">
+        <v>2</v>
+      </c>
+      <c r="G73" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="4"/>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="8"/>
+      <c r="G75" s="8"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G77">
@@ -3134,15 +3164,14 @@
         <v>9</v>
       </c>
       <c r="C2" s="2">
-        <f>COUNTIF(GROUP1!D:D,B2)+COUNTIF(GROUP1!E:E,B2)</f>
         <v>3</v>
       </c>
       <c r="D2" s="2" cm="1">
-        <f t="array" ref="D2">SUMPRODUCT((GROUP1!$D$2:$D$73=B2)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B2)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D2">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B2)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B2)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E2" s="2" cm="1">
-        <f t="array" ref="E2">SUMPRODUCT(((GROUP1!$D$2:$D$73=B2)+(GROUP1!$E$2:$E$73=B2))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E2">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B2)+('GROUP 1'!$E$2:$E$73=B2))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F2" s="2">
@@ -3150,11 +3179,11 @@
         <v>1</v>
       </c>
       <c r="G2" s="2">
-        <f>SUMIF(GROUP1!D:D,B2,GROUP1!F:F)+SUMIF(GROUP1!E:E,B2,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B2,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B2,'GROUP 1'!G:G)</f>
         <v>6</v>
       </c>
       <c r="H2" s="2">
-        <f>SUMIF(GROUP1!D:D,B2,GROUP1!G:G)+SUMIF(GROUP1!E:E,B2,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B2,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B2,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I2" s="2">
@@ -3175,15 +3204,15 @@
         <v>10</v>
       </c>
       <c r="C3" s="2">
-        <f>COUNTIF(GROUP1!D:D,B3)+COUNTIF(GROUP1!E:E,B3)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B3)+COUNTIF('GROUP 1'!E:E,B3)</f>
         <v>3</v>
       </c>
       <c r="D3" s="2" cm="1">
-        <f t="array" ref="D3">SUMPRODUCT((GROUP1!$D$2:$D$73=B3)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B3)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D3">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B3)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B3)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E3" s="2" cm="1">
-        <f t="array" ref="E3">SUMPRODUCT(((GROUP1!$D$2:$D$73=B3)+(GROUP1!$E$2:$E$73=B3))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E3">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B3)+('GROUP 1'!$E$2:$E$73=B3))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F3" s="2">
@@ -3191,11 +3220,11 @@
         <v>0</v>
       </c>
       <c r="G3" s="2">
-        <f>SUMIF(GROUP1!D:D,B3,GROUP1!F:F)+SUMIF(GROUP1!E:E,B3,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B3,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B3,'GROUP 1'!G:G)</f>
         <v>5</v>
       </c>
       <c r="H3" s="2">
-        <f>SUMIF(GROUP1!D:D,B3,GROUP1!G:G)+SUMIF(GROUP1!E:E,B3,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B3,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B3,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I3" s="2">
@@ -3216,15 +3245,15 @@
         <v>11</v>
       </c>
       <c r="C4" s="2">
-        <f>COUNTIF(GROUP1!D:D,B4)+COUNTIF(GROUP1!E:E,B4)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B4)+COUNTIF('GROUP 1'!E:E,B4)</f>
         <v>3</v>
       </c>
       <c r="D4" s="2" cm="1">
-        <f t="array" ref="D4">SUMPRODUCT((GROUP1!$D$2:$D$73=B4)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B4)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D4">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B4)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B4)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E4" s="2" cm="1">
-        <f t="array" ref="E4">SUMPRODUCT(((GROUP1!$D$2:$D$73=B4)+(GROUP1!$E$2:$E$73=B4))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E4">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B4)+('GROUP 1'!$E$2:$E$73=B4))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F4" s="2">
@@ -3232,11 +3261,11 @@
         <v>2</v>
       </c>
       <c r="G4" s="2">
-        <f>SUMIF(GROUP1!D:D,B4,GROUP1!F:F)+SUMIF(GROUP1!E:E,B4,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B4,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B4,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H4" s="2">
-        <f>SUMIF(GROUP1!D:D,B4,GROUP1!G:G)+SUMIF(GROUP1!E:E,B4,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B4,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B4,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I4" s="2">
@@ -3256,15 +3285,15 @@
         <v>12</v>
       </c>
       <c r="C5" s="2">
-        <f>COUNTIF(GROUP1!D:D,B5)+COUNTIF(GROUP1!E:E,B5)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B5)+COUNTIF('GROUP 1'!E:E,B5)</f>
         <v>3</v>
       </c>
       <c r="D5" s="2" cm="1">
-        <f t="array" ref="D5">SUMPRODUCT((GROUP1!$D$2:$D$73=B5)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B5)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D5">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B5)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B5)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E5" s="2" cm="1">
-        <f t="array" ref="E5">SUMPRODUCT(((GROUP1!$D$2:$D$73=B5)+(GROUP1!$E$2:$E$73=B5))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E5">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B5)+('GROUP 1'!$E$2:$E$73=B5))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F5" s="2">
@@ -3272,11 +3301,11 @@
         <v>2</v>
       </c>
       <c r="G5" s="2">
-        <f>SUMIF(GROUP1!D:D,B5,GROUP1!F:F)+SUMIF(GROUP1!E:E,B5,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B5,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B5,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H5" s="2">
-        <f>SUMIF(GROUP1!D:D,B5,GROUP1!G:G)+SUMIF(GROUP1!E:E,B5,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B5,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B5,'GROUP 1'!F:F)</f>
         <v>6</v>
       </c>
       <c r="I5" s="2">
@@ -3296,15 +3325,15 @@
         <v>29</v>
       </c>
       <c r="C6" s="2">
-        <f>COUNTIF(GROUP1!D:D,B6)+COUNTIF(GROUP1!E:E,B6)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B6)+COUNTIF('GROUP 1'!E:E,B6)</f>
         <v>3</v>
       </c>
       <c r="D6" s="2" cm="1">
-        <f t="array" ref="D6">SUMPRODUCT((GROUP1!$D$2:$D$73=B6)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B6)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D6">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B6)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B6)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E6" s="2" cm="1">
-        <f t="array" ref="E6">SUMPRODUCT(((GROUP1!$D$2:$D$73=B6)+(GROUP1!$E$2:$E$73=B6))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E6">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B6)+('GROUP 1'!$E$2:$E$73=B6))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F6" s="2">
@@ -3312,11 +3341,11 @@
         <v>0</v>
       </c>
       <c r="G6" s="2">
-        <f>SUMIF(GROUP1!D:D,B6,GROUP1!F:F)+SUMIF(GROUP1!E:E,B6,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B6,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B6,'GROUP 1'!G:G)</f>
         <v>7</v>
       </c>
       <c r="H6" s="2">
-        <f>SUMIF(GROUP1!D:D,B6,GROUP1!G:G)+SUMIF(GROUP1!E:E,B6,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B6,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B6,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I6" s="2">
@@ -3337,15 +3366,15 @@
         <v>26</v>
       </c>
       <c r="C7" s="2">
-        <f>COUNTIF(GROUP1!D:D,B7)+COUNTIF(GROUP1!E:E,B7)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B7)+COUNTIF('GROUP 1'!E:E,B7)</f>
         <v>3</v>
       </c>
       <c r="D7" s="2" cm="1">
-        <f t="array" ref="D7">SUMPRODUCT((GROUP1!$D$2:$D$73=B7)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B7)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D7">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B7)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B7)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E7" s="2" cm="1">
-        <f t="array" ref="E7">SUMPRODUCT(((GROUP1!$D$2:$D$73=B7)+(GROUP1!$E$2:$E$73=B7))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E7">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B7)+('GROUP 1'!$E$2:$E$73=B7))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F7" s="2">
@@ -3353,11 +3382,11 @@
         <v>1</v>
       </c>
       <c r="G7" s="2">
-        <f>SUMIF(GROUP1!D:D,B7,GROUP1!F:F)+SUMIF(GROUP1!E:E,B7,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B7,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B7,'GROUP 1'!G:G)</f>
         <v>8</v>
       </c>
       <c r="H7" s="2">
-        <f>SUMIF(GROUP1!D:D,B7,GROUP1!G:G)+SUMIF(GROUP1!E:E,B7,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B7,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B7,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I7" s="2">
@@ -3378,15 +3407,15 @@
         <v>27</v>
       </c>
       <c r="C8" s="2">
-        <f>COUNTIF(GROUP1!D:D,B8)+COUNTIF(GROUP1!E:E,B8)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B8)+COUNTIF('GROUP 1'!E:E,B8)</f>
         <v>3</v>
       </c>
       <c r="D8" s="2" cm="1">
-        <f t="array" ref="D8">SUMPRODUCT((GROUP1!$D$2:$D$73=B8)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B8)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D8">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B8)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B8)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E8" s="2" cm="1">
-        <f t="array" ref="E8">SUMPRODUCT(((GROUP1!$D$2:$D$73=B8)+(GROUP1!$E$2:$E$73=B8))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E8">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B8)+('GROUP 1'!$E$2:$E$73=B8))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F8" s="2">
@@ -3394,11 +3423,11 @@
         <v>1</v>
       </c>
       <c r="G8" s="2">
-        <f>SUMIF(GROUP1!D:D,B8,GROUP1!F:F)+SUMIF(GROUP1!E:E,B8,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B8,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B8,'GROUP 1'!G:G)</f>
         <v>5</v>
       </c>
       <c r="H8" s="2">
-        <f>SUMIF(GROUP1!D:D,B8,GROUP1!G:G)+SUMIF(GROUP1!E:E,B8,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B8,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B8,'GROUP 1'!F:F)</f>
         <v>6</v>
       </c>
       <c r="I8" s="2">
@@ -3419,15 +3448,15 @@
         <v>30</v>
       </c>
       <c r="C9" s="2">
-        <f>COUNTIF(GROUP1!D:D,B9)+COUNTIF(GROUP1!E:E,B9)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B9)+COUNTIF('GROUP 1'!E:E,B9)</f>
         <v>3</v>
       </c>
       <c r="D9" s="2" cm="1">
-        <f t="array" ref="D9">SUMPRODUCT((GROUP1!$D$2:$D$73=B9)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B9)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D9">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B9)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B9)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E9" s="2" cm="1">
-        <f t="array" ref="E9">SUMPRODUCT(((GROUP1!$D$2:$D$73=B9)+(GROUP1!$E$2:$E$73=B9))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E9">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B9)+('GROUP 1'!$E$2:$E$73=B9))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F9" s="2">
@@ -3435,11 +3464,11 @@
         <v>2</v>
       </c>
       <c r="G9" s="2">
-        <f>SUMIF(GROUP1!D:D,B9,GROUP1!F:F)+SUMIF(GROUP1!E:E,B9,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B9,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B9,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H9" s="2">
-        <f>SUMIF(GROUP1!D:D,B9,GROUP1!G:G)+SUMIF(GROUP1!E:E,B9,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B9,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B9,'GROUP 1'!F:F)</f>
         <v>10</v>
       </c>
       <c r="I9" s="2">
@@ -3460,15 +3489,15 @@
         <v>32</v>
       </c>
       <c r="C10" s="2">
-        <f>COUNTIF(GROUP1!D:D,B10)+COUNTIF(GROUP1!E:E,B10)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B10)+COUNTIF('GROUP 1'!E:E,B10)</f>
         <v>3</v>
       </c>
       <c r="D10" s="2" cm="1">
-        <f t="array" ref="D10">SUMPRODUCT((GROUP1!$D$2:$D$73=B10)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B10)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D10">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B10)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B10)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E10" s="2" cm="1">
-        <f t="array" ref="E10">SUMPRODUCT(((GROUP1!$D$2:$D$73=B10)+(GROUP1!$E$2:$E$73=B10))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E10">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B10)+('GROUP 1'!$E$2:$E$73=B10))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F10" s="2">
@@ -3476,11 +3505,11 @@
         <v>0</v>
       </c>
       <c r="G10" s="2">
-        <f>SUMIF(GROUP1!D:D,B10,GROUP1!F:F)+SUMIF(GROUP1!E:E,B10,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B10,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B10,'GROUP 1'!G:G)</f>
         <v>7</v>
       </c>
       <c r="H10" s="2">
-        <f>SUMIF(GROUP1!D:D,B10,GROUP1!G:G)+SUMIF(GROUP1!E:E,B10,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B10,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B10,'GROUP 1'!F:F)</f>
         <v>1</v>
       </c>
       <c r="I10" s="2">
@@ -3501,15 +3530,15 @@
         <v>33</v>
       </c>
       <c r="C11" s="2">
-        <f>COUNTIF(GROUP1!D:D,B11)+COUNTIF(GROUP1!E:E,B11)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B11)+COUNTIF('GROUP 1'!E:E,B11)</f>
         <v>3</v>
       </c>
       <c r="D11" s="2" cm="1">
-        <f t="array" ref="D11">SUMPRODUCT((GROUP1!$D$2:$D$73=B11)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B11)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D11">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B11)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B11)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E11" s="2" cm="1">
-        <f t="array" ref="E11">SUMPRODUCT(((GROUP1!$D$2:$D$73=B11)+(GROUP1!$E$2:$E$73=B11))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E11">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B11)+('GROUP 1'!$E$2:$E$73=B11))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F11" s="2">
@@ -3517,11 +3546,11 @@
         <v>0</v>
       </c>
       <c r="G11" s="2">
-        <f>SUMIF(GROUP1!D:D,B11,GROUP1!F:F)+SUMIF(GROUP1!E:E,B11,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B11,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B11,'GROUP 1'!G:G)</f>
         <v>6</v>
       </c>
       <c r="H11" s="2">
-        <f>SUMIF(GROUP1!D:D,B11,GROUP1!G:G)+SUMIF(GROUP1!E:E,B11,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B11,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B11,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I11" s="2">
@@ -3542,15 +3571,15 @@
         <v>34</v>
       </c>
       <c r="C12" s="2">
-        <f>COUNTIF(GROUP1!D:D,B12)+COUNTIF(GROUP1!E:E,B12)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B12)+COUNTIF('GROUP 1'!E:E,B12)</f>
         <v>3</v>
       </c>
       <c r="D12" s="2" cm="1">
-        <f t="array" ref="D12">SUMPRODUCT((GROUP1!$D$2:$D$73=B12)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B12)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D12">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B12)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B12)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E12" s="2" cm="1">
-        <f t="array" ref="E12">SUMPRODUCT(((GROUP1!$D$2:$D$73=B12)+(GROUP1!$E$2:$E$73=B12))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E12">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B12)+('GROUP 1'!$E$2:$E$73=B12))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F12" s="2">
@@ -3558,11 +3587,11 @@
         <v>2</v>
       </c>
       <c r="G12" s="2">
-        <f>SUMIF(GROUP1!D:D,B12,GROUP1!F:F)+SUMIF(GROUP1!E:E,B12,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B12,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B12,'GROUP 1'!G:G)</f>
         <v>1</v>
       </c>
       <c r="H12" s="2">
-        <f>SUMIF(GROUP1!D:D,B12,GROUP1!G:G)+SUMIF(GROUP1!E:E,B12,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B12,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B12,'GROUP 1'!F:F)</f>
         <v>4</v>
       </c>
       <c r="I12" s="2">
@@ -3583,15 +3612,15 @@
         <v>35</v>
       </c>
       <c r="C13" s="2">
-        <f>COUNTIF(GROUP1!D:D,B13)+COUNTIF(GROUP1!E:E,B13)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B13)+COUNTIF('GROUP 1'!E:E,B13)</f>
         <v>3</v>
       </c>
       <c r="D13" s="2" cm="1">
-        <f t="array" ref="D13">SUMPRODUCT((GROUP1!$D$2:$D$73=B13)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B13)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D13">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B13)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B13)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E13" s="2" cm="1">
-        <f t="array" ref="E13">SUMPRODUCT(((GROUP1!$D$2:$D$73=B13)+(GROUP1!$E$2:$E$73=B13))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E13">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B13)+('GROUP 1'!$E$2:$E$73=B13))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F13" s="2">
@@ -3599,11 +3628,11 @@
         <v>3</v>
       </c>
       <c r="G13" s="2">
-        <f>SUMIF(GROUP1!D:D,B13,GROUP1!F:F)+SUMIF(GROUP1!E:E,B13,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B13,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B13,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H13" s="2">
-        <f>SUMIF(GROUP1!D:D,B13,GROUP1!G:G)+SUMIF(GROUP1!E:E,B13,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B13,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B13,'GROUP 1'!F:F)</f>
         <v>8</v>
       </c>
       <c r="I13" s="2">
@@ -3624,15 +3653,15 @@
         <v>38</v>
       </c>
       <c r="C14" s="2">
-        <f>COUNTIF(GROUP1!D:D,B14)+COUNTIF(GROUP1!E:E,B14)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B14)+COUNTIF('GROUP 1'!E:E,B14)</f>
         <v>3</v>
       </c>
       <c r="D14" s="2" cm="1">
-        <f t="array" ref="D14">SUMPRODUCT((GROUP1!$D$2:$D$73=B14)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B14)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D14">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B14)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B14)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E14" s="2" cm="1">
-        <f t="array" ref="E14">SUMPRODUCT(((GROUP1!$D$2:$D$73=B14)+(GROUP1!$E$2:$E$73=B14))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E14">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B14)+('GROUP 1'!$E$2:$E$73=B14))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F14" s="2">
@@ -3640,11 +3669,11 @@
         <v>1</v>
       </c>
       <c r="G14" s="2">
-        <f>SUMIF(GROUP1!D:D,B14,GROUP1!F:F)+SUMIF(GROUP1!E:E,B14,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B14,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B14,'GROUP 1'!G:G)</f>
         <v>8</v>
       </c>
       <c r="H14" s="2">
-        <f>SUMIF(GROUP1!D:D,B14,GROUP1!G:G)+SUMIF(GROUP1!E:E,B14,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B14,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B14,'GROUP 1'!F:F)</f>
         <v>4</v>
       </c>
       <c r="I14" s="2">
@@ -3665,15 +3694,15 @@
         <v>40</v>
       </c>
       <c r="C15" s="2">
-        <f>COUNTIF(GROUP1!D:D,B15)+COUNTIF(GROUP1!E:E,B15)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B15)+COUNTIF('GROUP 1'!E:E,B15)</f>
         <v>3</v>
       </c>
       <c r="D15" s="2" cm="1">
-        <f t="array" ref="D15">SUMPRODUCT((GROUP1!$D$2:$D$73=B15)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B15)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D15">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B15)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B15)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E15" s="2" cm="1">
-        <f t="array" ref="E15">SUMPRODUCT(((GROUP1!$D$2:$D$73=B15)+(GROUP1!$E$2:$E$73=B15))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E15">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B15)+('GROUP 1'!$E$2:$E$73=B15))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F15" s="2">
@@ -3681,11 +3710,11 @@
         <v>1</v>
       </c>
       <c r="G15" s="2">
-        <f>SUMIF(GROUP1!D:D,B15,GROUP1!F:F)+SUMIF(GROUP1!E:E,B15,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B15,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B15,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H15" s="2">
-        <f>SUMIF(GROUP1!D:D,B15,GROUP1!G:G)+SUMIF(GROUP1!E:E,B15,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B15,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B15,'GROUP 1'!F:F)</f>
         <v>2</v>
       </c>
       <c r="I15" s="2">
@@ -3706,15 +3735,15 @@
         <v>41</v>
       </c>
       <c r="C16" s="2">
-        <f>COUNTIF(GROUP1!D:D,B16)+COUNTIF(GROUP1!E:E,B16)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B16)+COUNTIF('GROUP 1'!E:E,B16)</f>
         <v>3</v>
       </c>
       <c r="D16" s="2" cm="1">
-        <f t="array" ref="D16">SUMPRODUCT((GROUP1!$D$2:$D$73=B16)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B16)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D16">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B16)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B16)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E16" s="2" cm="1">
-        <f t="array" ref="E16">SUMPRODUCT(((GROUP1!$D$2:$D$73=B16)+(GROUP1!$E$2:$E$73=B16))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E16">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B16)+('GROUP 1'!$E$2:$E$73=B16))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F16" s="2">
@@ -3722,11 +3751,11 @@
         <v>2</v>
       </c>
       <c r="G16" s="2">
-        <f>SUMIF(GROUP1!D:D,B16,GROUP1!F:F)+SUMIF(GROUP1!E:E,B16,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B16,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B16,'GROUP 1'!G:G)</f>
         <v>3</v>
       </c>
       <c r="H16" s="2">
-        <f>SUMIF(GROUP1!D:D,B16,GROUP1!G:G)+SUMIF(GROUP1!E:E,B16,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B16,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B16,'GROUP 1'!F:F)</f>
         <v>5</v>
       </c>
       <c r="I16" s="2">
@@ -3747,15 +3776,15 @@
         <v>39</v>
       </c>
       <c r="C17" s="2">
-        <f>COUNTIF(GROUP1!D:D,B17)+COUNTIF(GROUP1!E:E,B17)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B17)+COUNTIF('GROUP 1'!E:E,B17)</f>
         <v>3</v>
       </c>
       <c r="D17" s="2" cm="1">
-        <f t="array" ref="D17">SUMPRODUCT((GROUP1!$D$2:$D$73=B17)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B17)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D17">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B17)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B17)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E17" s="2" cm="1">
-        <f t="array" ref="E17">SUMPRODUCT(((GROUP1!$D$2:$D$73=B17)+(GROUP1!$E$2:$E$73=B17))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E17">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B17)+('GROUP 1'!$E$2:$E$73=B17))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F17" s="2">
@@ -3763,11 +3792,11 @@
         <v>1</v>
       </c>
       <c r="G17" s="2">
-        <f>SUMIF(GROUP1!D:D,B17,GROUP1!F:F)+SUMIF(GROUP1!E:E,B17,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B17,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B17,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H17" s="2">
-        <f>SUMIF(GROUP1!D:D,B17,GROUP1!G:G)+SUMIF(GROUP1!E:E,B17,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B17,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B17,'GROUP 1'!F:F)</f>
         <v>4</v>
       </c>
       <c r="I17" s="2">
@@ -3788,15 +3817,15 @@
         <v>45</v>
       </c>
       <c r="C18" s="2">
-        <f>COUNTIF(GROUP1!D:D,B18)+COUNTIF(GROUP1!E:E,B18)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B18)+COUNTIF('GROUP 1'!E:E,B18)</f>
         <v>3</v>
       </c>
       <c r="D18" s="2" cm="1">
-        <f t="array" ref="D18">SUMPRODUCT((GROUP1!$D$2:$D$73=B18)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B18)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D18">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B18)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B18)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E18" s="2" cm="1">
-        <f t="array" ref="E18">SUMPRODUCT(((GROUP1!$D$2:$D$73=B18)+(GROUP1!$E$2:$E$73=B18))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E18">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B18)+('GROUP 1'!$E$2:$E$73=B18))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F18" s="2">
@@ -3804,11 +3833,11 @@
         <v>1</v>
       </c>
       <c r="G18" s="2">
-        <f>SUMIF(GROUP1!D:D,B18,GROUP1!F:F)+SUMIF(GROUP1!E:E,B18,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B18,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B18,'GROUP 1'!G:G)</f>
         <v>10</v>
       </c>
       <c r="H18" s="2">
-        <f>SUMIF(GROUP1!D:D,B18,GROUP1!G:G)+SUMIF(GROUP1!E:E,B18,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B18,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B18,'GROUP 1'!F:F)</f>
         <v>4</v>
       </c>
       <c r="I18" s="2">
@@ -3829,15 +3858,15 @@
         <v>47</v>
       </c>
       <c r="C19" s="2">
-        <f>COUNTIF(GROUP1!D:D,B19)+COUNTIF(GROUP1!E:E,B19)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B19)+COUNTIF('GROUP 1'!E:E,B19)</f>
         <v>3</v>
       </c>
       <c r="D19" s="2" cm="1">
-        <f t="array" ref="D19">SUMPRODUCT((GROUP1!$D$2:$D$73=B19)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B19)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D19">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B19)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B19)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E19" s="2" cm="1">
-        <f t="array" ref="E19">SUMPRODUCT(((GROUP1!$D$2:$D$73=B19)+(GROUP1!$E$2:$E$73=B19))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E19">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B19)+('GROUP 1'!$E$2:$E$73=B19))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F19" s="2">
@@ -3845,11 +3874,11 @@
         <v>1</v>
       </c>
       <c r="G19" s="2">
-        <f>SUMIF(GROUP1!D:D,B19,GROUP1!F:F)+SUMIF(GROUP1!E:E,B19,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B19,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B19,'GROUP 1'!G:G)</f>
         <v>4</v>
       </c>
       <c r="H19" s="2">
-        <f>SUMIF(GROUP1!D:D,B19,GROUP1!G:G)+SUMIF(GROUP1!E:E,B19,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B19,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B19,'GROUP 1'!F:F)</f>
         <v>2</v>
       </c>
       <c r="I19" s="2">
@@ -3870,15 +3899,15 @@
         <v>48</v>
       </c>
       <c r="C20" s="2">
-        <f>COUNTIF(GROUP1!D:D,B20)+COUNTIF(GROUP1!E:E,B20)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B20)+COUNTIF('GROUP 1'!E:E,B20)</f>
         <v>3</v>
       </c>
       <c r="D20" s="2" cm="1">
-        <f t="array" ref="D20">SUMPRODUCT((GROUP1!$D$2:$D$73=B20)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B20)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D20">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B20)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B20)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E20" s="2" cm="1">
-        <f t="array" ref="E20">SUMPRODUCT(((GROUP1!$D$2:$D$73=B20)+(GROUP1!$E$2:$E$73=B20))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E20">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B20)+('GROUP 1'!$E$2:$E$73=B20))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F20" s="2">
@@ -3886,11 +3915,11 @@
         <v>1</v>
       </c>
       <c r="G20" s="2">
-        <f>SUMIF(GROUP1!D:D,B20,GROUP1!F:F)+SUMIF(GROUP1!E:E,B20,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B20,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B20,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H20" s="2">
-        <f>SUMIF(GROUP1!D:D,B20,GROUP1!G:G)+SUMIF(GROUP1!E:E,B20,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B20,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B20,'GROUP 1'!F:F)</f>
         <v>2</v>
       </c>
       <c r="I20" s="2">
@@ -3911,15 +3940,15 @@
         <v>46</v>
       </c>
       <c r="C21" s="2">
-        <f>COUNTIF(GROUP1!D:D,B21)+COUNTIF(GROUP1!E:E,B21)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B21)+COUNTIF('GROUP 1'!E:E,B21)</f>
         <v>3</v>
       </c>
       <c r="D21" s="2" cm="1">
-        <f t="array" ref="D21">SUMPRODUCT((GROUP1!$D$2:$D$73=B21)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B21)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D21">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B21)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B21)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E21" s="2" cm="1">
-        <f t="array" ref="E21">SUMPRODUCT(((GROUP1!$D$2:$D$73=B21)+(GROUP1!$E$2:$E$73=B21))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E21">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B21)+('GROUP 1'!$E$2:$E$73=B21))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F21" s="2">
@@ -3927,11 +3956,11 @@
         <v>2</v>
       </c>
       <c r="G21" s="2">
-        <f>SUMIF(GROUP1!D:D,B21,GROUP1!F:F)+SUMIF(GROUP1!E:E,B21,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B21,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B21,'GROUP 1'!G:G)</f>
         <v>1</v>
       </c>
       <c r="H21" s="2">
-        <f>SUMIF(GROUP1!D:D,B21,GROUP1!G:G)+SUMIF(GROUP1!E:E,B21,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B21,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B21,'GROUP 1'!F:F)</f>
         <v>9</v>
       </c>
       <c r="I21" s="2">
@@ -3952,15 +3981,15 @@
         <v>51</v>
       </c>
       <c r="C22" s="2">
-        <f>COUNTIF(GROUP1!D:D,B22)+COUNTIF(GROUP1!E:E,B22)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B22)+COUNTIF('GROUP 1'!E:E,B22)</f>
         <v>3</v>
       </c>
       <c r="D22" s="2" cm="1">
-        <f t="array" ref="D22">SUMPRODUCT((GROUP1!$D$2:$D$73=B22)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B22)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D22">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B22)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B22)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E22" s="2" cm="1">
-        <f t="array" ref="E22">SUMPRODUCT(((GROUP1!$D$2:$D$73=B22)+(GROUP1!$E$2:$E$73=B22))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E22">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B22)+('GROUP 1'!$E$2:$E$73=B22))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F22" s="2">
@@ -3968,11 +3997,11 @@
         <v>0</v>
       </c>
       <c r="G22" s="2">
-        <f>SUMIF(GROUP1!D:D,B22,GROUP1!F:F)+SUMIF(GROUP1!E:E,B22,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B22,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B22,'GROUP 1'!G:G)</f>
         <v>10</v>
       </c>
       <c r="H22" s="2">
-        <f>SUMIF(GROUP1!D:D,B22,GROUP1!G:G)+SUMIF(GROUP1!E:E,B22,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B22,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B22,'GROUP 1'!F:F)</f>
         <v>4</v>
       </c>
       <c r="I22" s="2">
@@ -3992,15 +4021,15 @@
         <v>52</v>
       </c>
       <c r="C23" s="2">
-        <f>COUNTIF(GROUP1!D:D,B23)+COUNTIF(GROUP1!E:E,B23)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B23)+COUNTIF('GROUP 1'!E:E,B23)</f>
         <v>3</v>
       </c>
       <c r="D23" s="2" cm="1">
-        <f t="array" ref="D23">SUMPRODUCT((GROUP1!$D$2:$D$73=B23)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B23)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D23">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B23)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B23)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E23" s="2" cm="1">
-        <f t="array" ref="E23">SUMPRODUCT(((GROUP1!$D$2:$D$73=B23)+(GROUP1!$E$2:$E$73=B23))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E23">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B23)+('GROUP 1'!$E$2:$E$73=B23))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>2</v>
       </c>
       <c r="F23" s="2">
@@ -4008,11 +4037,11 @@
         <v>0</v>
       </c>
       <c r="G23" s="2">
-        <f>SUMIF(GROUP1!D:D,B23,GROUP1!F:F)+SUMIF(GROUP1!E:E,B23,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B23,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B23,'GROUP 1'!G:G)</f>
         <v>7</v>
       </c>
       <c r="H23" s="2">
-        <f>SUMIF(GROUP1!D:D,B23,GROUP1!G:G)+SUMIF(GROUP1!E:E,B23,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B23,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B23,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I23" s="2">
@@ -4032,15 +4061,15 @@
         <v>53</v>
       </c>
       <c r="C24" s="2">
-        <f>COUNTIF(GROUP1!D:D,B24)+COUNTIF(GROUP1!E:E,B24)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B24)+COUNTIF('GROUP 1'!E:E,B24)</f>
         <v>3</v>
       </c>
       <c r="D24" s="2" cm="1">
-        <f t="array" ref="D24">SUMPRODUCT((GROUP1!$D$2:$D$73=B24)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B24)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D24">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B24)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B24)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E24" s="2" cm="1">
-        <f t="array" ref="E24">SUMPRODUCT(((GROUP1!$D$2:$D$73=B24)+(GROUP1!$E$2:$E$73=B24))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E24">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B24)+('GROUP 1'!$E$2:$E$73=B24))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F24" s="2">
@@ -4048,11 +4077,11 @@
         <v>1</v>
       </c>
       <c r="G24" s="2">
-        <f>SUMIF(GROUP1!D:D,B24,GROUP1!F:F)+SUMIF(GROUP1!E:E,B24,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B24,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B24,'GROUP 1'!G:G)</f>
         <v>7</v>
       </c>
       <c r="H24" s="2">
-        <f>SUMIF(GROUP1!D:D,B24,GROUP1!G:G)+SUMIF(GROUP1!E:E,B24,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B24,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B24,'GROUP 1'!F:F)</f>
         <v>7</v>
       </c>
       <c r="I24" s="2">
@@ -4073,15 +4102,15 @@
         <v>54</v>
       </c>
       <c r="C25" s="2">
-        <f>COUNTIF(GROUP1!D:D,B25)+COUNTIF(GROUP1!E:E,B25)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B25)+COUNTIF('GROUP 1'!E:E,B25)</f>
         <v>3</v>
       </c>
       <c r="D25" s="2" cm="1">
-        <f t="array" ref="D25">SUMPRODUCT((GROUP1!$D$2:$D$73=B25)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B25)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D25">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B25)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B25)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E25" s="2" cm="1">
-        <f t="array" ref="E25">SUMPRODUCT(((GROUP1!$D$2:$D$73=B25)+(GROUP1!$E$2:$E$73=B25))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E25">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B25)+('GROUP 1'!$E$2:$E$73=B25))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F25" s="2">
@@ -4089,11 +4118,11 @@
         <v>3</v>
       </c>
       <c r="G25" s="2">
-        <f>SUMIF(GROUP1!D:D,B25,GROUP1!F:F)+SUMIF(GROUP1!E:E,B25,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B25,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B25,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H25" s="2">
-        <f>SUMIF(GROUP1!D:D,B25,GROUP1!G:G)+SUMIF(GROUP1!E:E,B25,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B25,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B25,'GROUP 1'!F:F)</f>
         <v>12</v>
       </c>
       <c r="I25" s="2">
@@ -4114,15 +4143,15 @@
         <v>57</v>
       </c>
       <c r="C26" s="2">
-        <f>COUNTIF(GROUP1!D:D,B26)+COUNTIF(GROUP1!E:E,B26)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B26)+COUNTIF('GROUP 1'!E:E,B26)</f>
         <v>3</v>
       </c>
       <c r="D26" s="2" cm="1">
-        <f t="array" ref="D26">SUMPRODUCT((GROUP1!$D$2:$D$73=B26)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B26)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D26">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B26)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B26)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E26" s="2" cm="1">
-        <f t="array" ref="E26">SUMPRODUCT(((GROUP1!$D$2:$D$73=B26)+(GROUP1!$E$2:$E$73=B26))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E26">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B26)+('GROUP 1'!$E$2:$E$73=B26))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>2</v>
       </c>
       <c r="F26" s="2">
@@ -4130,11 +4159,11 @@
         <v>0</v>
       </c>
       <c r="G26" s="2">
-        <f>SUMIF(GROUP1!D:D,B26,GROUP1!F:F)+SUMIF(GROUP1!E:E,B26,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B26,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B26,'GROUP 1'!G:G)</f>
         <v>6</v>
       </c>
       <c r="H26" s="2">
-        <f>SUMIF(GROUP1!D:D,B26,GROUP1!G:G)+SUMIF(GROUP1!E:E,B26,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B26,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B26,'GROUP 1'!F:F)</f>
         <v>2</v>
       </c>
       <c r="I26" s="2">
@@ -4155,15 +4184,15 @@
         <v>58</v>
       </c>
       <c r="C27" s="2">
-        <f>COUNTIF(GROUP1!D:D,B27)+COUNTIF(GROUP1!E:E,B27)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B27)+COUNTIF('GROUP 1'!E:E,B27)</f>
         <v>3</v>
       </c>
       <c r="D27" s="2" cm="1">
-        <f t="array" ref="D27">SUMPRODUCT((GROUP1!$D$2:$D$73=B27)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B27)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D27">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B27)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B27)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E27" s="2" cm="1">
-        <f t="array" ref="E27">SUMPRODUCT(((GROUP1!$D$2:$D$73=B27)+(GROUP1!$E$2:$E$73=B27))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E27">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B27)+('GROUP 1'!$E$2:$E$73=B27))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>2</v>
       </c>
       <c r="F27" s="2">
@@ -4171,11 +4200,11 @@
         <v>0</v>
       </c>
       <c r="G27" s="2">
-        <f>SUMIF(GROUP1!D:D,B27,GROUP1!F:F)+SUMIF(GROUP1!E:E,B27,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B27,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B27,'GROUP 1'!G:G)</f>
         <v>5</v>
       </c>
       <c r="H27" s="2">
-        <f>SUMIF(GROUP1!D:D,B27,GROUP1!G:G)+SUMIF(GROUP1!E:E,B27,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B27,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B27,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I27" s="2">
@@ -4196,15 +4225,15 @@
         <v>59</v>
       </c>
       <c r="C28" s="2">
-        <f>COUNTIF(GROUP1!D:D,B28)+COUNTIF(GROUP1!E:E,B28)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B28)+COUNTIF('GROUP 1'!E:E,B28)</f>
         <v>3</v>
       </c>
       <c r="D28" s="2" cm="1">
-        <f t="array" ref="D28">SUMPRODUCT((GROUP1!$D$2:$D$73=B28)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B28)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D28">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B28)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B28)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E28" s="2" cm="1">
-        <f t="array" ref="E28">SUMPRODUCT(((GROUP1!$D$2:$D$73=B28)+(GROUP1!$E$2:$E$73=B28))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E28">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B28)+('GROUP 1'!$E$2:$E$73=B28))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>3</v>
       </c>
       <c r="F28" s="2">
@@ -4212,11 +4241,11 @@
         <v>0</v>
       </c>
       <c r="G28" s="2">
-        <f>SUMIF(GROUP1!D:D,B28,GROUP1!F:F)+SUMIF(GROUP1!E:E,B28,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B28,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B28,'GROUP 1'!G:G)</f>
         <v>3</v>
       </c>
       <c r="H28" s="2">
-        <f>SUMIF(GROUP1!D:D,B28,GROUP1!G:G)+SUMIF(GROUP1!E:E,B28,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B28,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B28,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I28" s="2">
@@ -4237,15 +4266,15 @@
         <v>60</v>
       </c>
       <c r="C29" s="2">
-        <f>COUNTIF(GROUP1!D:D,B29)+COUNTIF(GROUP1!E:E,B29)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B29)+COUNTIF('GROUP 1'!E:E,B29)</f>
         <v>3</v>
       </c>
       <c r="D29" s="2" cm="1">
-        <f t="array" ref="D29">SUMPRODUCT((GROUP1!$D$2:$D$73=B29)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B29)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D29">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B29)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B29)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E29" s="2" cm="1">
-        <f t="array" ref="E29">SUMPRODUCT(((GROUP1!$D$2:$D$73=B29)+(GROUP1!$E$2:$E$73=B29))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E29">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B29)+('GROUP 1'!$E$2:$E$73=B29))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F29" s="2">
@@ -4253,11 +4282,11 @@
         <v>2</v>
       </c>
       <c r="G29" s="2">
-        <f>SUMIF(GROUP1!D:D,B29,GROUP1!F:F)+SUMIF(GROUP1!E:E,B29,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B29,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B29,'GROUP 1'!G:G)</f>
         <v>4</v>
       </c>
       <c r="H29" s="2">
-        <f>SUMIF(GROUP1!D:D,B29,GROUP1!G:G)+SUMIF(GROUP1!E:E,B29,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B29,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B29,'GROUP 1'!F:F)</f>
         <v>10</v>
       </c>
       <c r="I29" s="2">
@@ -4278,15 +4307,15 @@
         <v>64</v>
       </c>
       <c r="C30" s="2">
-        <f>COUNTIF(GROUP1!D:D,B30)+COUNTIF(GROUP1!E:E,B30)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B30)+COUNTIF('GROUP 1'!E:E,B30)</f>
         <v>3</v>
       </c>
       <c r="D30" s="2" cm="1">
-        <f t="array" ref="D30">SUMPRODUCT((GROUP1!$D$2:$D$73=B30)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B30)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D30">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B30)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B30)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E30" s="2" cm="1">
-        <f t="array" ref="E30">SUMPRODUCT(((GROUP1!$D$2:$D$73=B30)+(GROUP1!$E$2:$E$73=B30))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E30">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B30)+('GROUP 1'!$E$2:$E$73=B30))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F30" s="2">
@@ -4294,11 +4323,11 @@
         <v>0</v>
       </c>
       <c r="G30" s="2">
-        <f>SUMIF(GROUP1!D:D,B30,GROUP1!F:F)+SUMIF(GROUP1!E:E,B30,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B30,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B30,'GROUP 1'!G:G)</f>
         <v>5</v>
       </c>
       <c r="H30" s="2">
-        <f>SUMIF(GROUP1!D:D,B30,GROUP1!G:G)+SUMIF(GROUP1!E:E,B30,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B30,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B30,'GROUP 1'!F:F)</f>
         <v>0</v>
       </c>
       <c r="I30" s="2">
@@ -4319,15 +4348,15 @@
         <v>65</v>
       </c>
       <c r="C31" s="2">
-        <f>COUNTIF(GROUP1!D:D,B31)+COUNTIF(GROUP1!E:E,B31)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B31)+COUNTIF('GROUP 1'!E:E,B31)</f>
         <v>3</v>
       </c>
       <c r="D31" s="2" cm="1">
-        <f t="array" ref="D31">SUMPRODUCT((GROUP1!$D$2:$D$73=B31)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B31)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D31">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B31)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B31)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E31" s="2" cm="1">
-        <f t="array" ref="E31">SUMPRODUCT(((GROUP1!$D$2:$D$73=B31)+(GROUP1!$E$2:$E$73=B31))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E31">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B31)+('GROUP 1'!$E$2:$E$73=B31))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>3</v>
       </c>
       <c r="F31" s="2">
@@ -4335,11 +4364,11 @@
         <v>0</v>
       </c>
       <c r="G31" s="2">
-        <f>SUMIF(GROUP1!D:D,B31,GROUP1!F:F)+SUMIF(GROUP1!E:E,B31,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B31,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B31,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H31" s="2">
-        <f>SUMIF(GROUP1!D:D,B31,GROUP1!G:G)+SUMIF(GROUP1!E:E,B31,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B31,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B31,'GROUP 1'!F:F)</f>
         <v>2</v>
       </c>
       <c r="I31" s="2">
@@ -4360,15 +4389,15 @@
         <v>66</v>
       </c>
       <c r="C32" s="2">
-        <f>COUNTIF(GROUP1!D:D,B32)+COUNTIF(GROUP1!E:E,B32)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B32)+COUNTIF('GROUP 1'!E:E,B32)</f>
         <v>3</v>
       </c>
       <c r="D32" s="2" cm="1">
-        <f t="array" ref="D32">SUMPRODUCT((GROUP1!$D$2:$D$73=B32)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B32)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D32">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B32)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B32)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E32" s="2" cm="1">
-        <f t="array" ref="E32">SUMPRODUCT(((GROUP1!$D$2:$D$73=B32)+(GROUP1!$E$2:$E$73=B32))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E32">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B32)+('GROUP 1'!$E$2:$E$73=B32))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>2</v>
       </c>
       <c r="F32" s="2">
@@ -4376,11 +4405,11 @@
         <v>1</v>
       </c>
       <c r="G32" s="2">
-        <f>SUMIF(GROUP1!D:D,B32,GROUP1!F:F)+SUMIF(GROUP1!E:E,B32,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B32,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B32,'GROUP 1'!G:G)</f>
         <v>1</v>
       </c>
       <c r="H32" s="2">
-        <f>SUMIF(GROUP1!D:D,B32,GROUP1!G:G)+SUMIF(GROUP1!E:E,B32,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B32,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B32,'GROUP 1'!F:F)</f>
         <v>5</v>
       </c>
       <c r="I32" s="2">
@@ -4401,15 +4430,15 @@
         <v>67</v>
       </c>
       <c r="C33" s="2">
-        <f>COUNTIF(GROUP1!D:D,B33)+COUNTIF(GROUP1!E:E,B33)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B33)+COUNTIF('GROUP 1'!E:E,B33)</f>
         <v>3</v>
       </c>
       <c r="D33" s="2" cm="1">
-        <f t="array" ref="D33">SUMPRODUCT((GROUP1!$D$2:$D$73=B33)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B33)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D33">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B33)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B33)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E33" s="2" cm="1">
-        <f t="array" ref="E33">SUMPRODUCT(((GROUP1!$D$2:$D$73=B33)+(GROUP1!$E$2:$E$73=B33))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E33">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B33)+('GROUP 1'!$E$2:$E$73=B33))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>2</v>
       </c>
       <c r="F33" s="2">
@@ -4417,11 +4446,11 @@
         <v>1</v>
       </c>
       <c r="G33" s="2">
-        <f>SUMIF(GROUP1!D:D,B33,GROUP1!F:F)+SUMIF(GROUP1!E:E,B33,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B33,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B33,'GROUP 1'!G:G)</f>
         <v>3</v>
       </c>
       <c r="H33" s="2">
-        <f>SUMIF(GROUP1!D:D,B33,GROUP1!G:G)+SUMIF(GROUP1!E:E,B33,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B33,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B33,'GROUP 1'!F:F)</f>
         <v>4</v>
       </c>
       <c r="I33" s="2">
@@ -4442,15 +4471,15 @@
         <v>70</v>
       </c>
       <c r="C34" s="2">
-        <f>COUNTIF(GROUP1!D:D,B34)+COUNTIF(GROUP1!E:E,B34)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B34)+COUNTIF('GROUP 1'!E:E,B34)</f>
         <v>3</v>
       </c>
       <c r="D34" s="2" cm="1">
-        <f t="array" ref="D34">SUMPRODUCT((GROUP1!$D$2:$D$73=B34)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B34)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D34">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B34)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B34)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>3</v>
       </c>
       <c r="E34" s="2" cm="1">
-        <f t="array" ref="E34">SUMPRODUCT(((GROUP1!$D$2:$D$73=B34)+(GROUP1!$E$2:$E$73=B34))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E34">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B34)+('GROUP 1'!$E$2:$E$73=B34))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F34" s="2">
@@ -4458,11 +4487,11 @@
         <v>0</v>
       </c>
       <c r="G34" s="2">
-        <f>SUMIF(GROUP1!D:D,B34,GROUP1!F:F)+SUMIF(GROUP1!E:E,B34,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B34,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B34,'GROUP 1'!G:G)</f>
         <v>10</v>
       </c>
       <c r="H34" s="2">
-        <f>SUMIF(GROUP1!D:D,B34,GROUP1!G:G)+SUMIF(GROUP1!E:E,B34,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B34,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B34,'GROUP 1'!F:F)</f>
         <v>2</v>
       </c>
       <c r="I34" s="2">
@@ -4483,15 +4512,15 @@
         <v>72</v>
       </c>
       <c r="C35" s="2">
-        <f>COUNTIF(GROUP1!D:D,B35)+COUNTIF(GROUP1!E:E,B35)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B35)+COUNTIF('GROUP 1'!E:E,B35)</f>
         <v>3</v>
       </c>
       <c r="D35" s="2" cm="1">
-        <f t="array" ref="D35">SUMPRODUCT((GROUP1!$D$2:$D$73=B35)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B35)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D35">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B35)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B35)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E35" s="2" cm="1">
-        <f t="array" ref="E35">SUMPRODUCT(((GROUP1!$D$2:$D$73=B35)+(GROUP1!$E$2:$E$73=B35))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E35">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B35)+('GROUP 1'!$E$2:$E$73=B35))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F35" s="2">
@@ -4499,11 +4528,11 @@
         <v>1</v>
       </c>
       <c r="G35" s="2">
-        <f>SUMIF(GROUP1!D:D,B35,GROUP1!F:F)+SUMIF(GROUP1!E:E,B35,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B35,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B35,'GROUP 1'!G:G)</f>
         <v>8</v>
       </c>
       <c r="H35" s="2">
-        <f>SUMIF(GROUP1!D:D,B35,GROUP1!G:G)+SUMIF(GROUP1!E:E,B35,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B35,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B35,'GROUP 1'!F:F)</f>
         <v>7</v>
       </c>
       <c r="I35" s="2">
@@ -4524,15 +4553,15 @@
         <v>71</v>
       </c>
       <c r="C36" s="2">
-        <f>COUNTIF(GROUP1!D:D,B36)+COUNTIF(GROUP1!E:E,B36)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B36)+COUNTIF('GROUP 1'!E:E,B36)</f>
         <v>3</v>
       </c>
       <c r="D36" s="2" cm="1">
-        <f t="array" ref="D36">SUMPRODUCT((GROUP1!$D$2:$D$73=B36)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B36)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D36">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B36)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B36)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E36" s="2" cm="1">
-        <f t="array" ref="E36">SUMPRODUCT(((GROUP1!$D$2:$D$73=B36)+(GROUP1!$E$2:$E$73=B36))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E36">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B36)+('GROUP 1'!$E$2:$E$73=B36))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F36" s="2">
@@ -4540,11 +4569,11 @@
         <v>2</v>
       </c>
       <c r="G36" s="2">
-        <f>SUMIF(GROUP1!D:D,B36,GROUP1!F:F)+SUMIF(GROUP1!E:E,B36,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B36,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B36,'GROUP 1'!G:G)</f>
         <v>8</v>
       </c>
       <c r="H36" s="2">
-        <f>SUMIF(GROUP1!D:D,B36,GROUP1!G:G)+SUMIF(GROUP1!E:E,B36,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B36,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B36,'GROUP 1'!F:F)</f>
         <v>6</v>
       </c>
       <c r="I36" s="2">
@@ -4565,15 +4594,15 @@
         <v>73</v>
       </c>
       <c r="C37" s="2">
-        <f>COUNTIF(GROUP1!D:D,B37)+COUNTIF(GROUP1!E:E,B37)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B37)+COUNTIF('GROUP 1'!E:E,B37)</f>
         <v>3</v>
       </c>
       <c r="D37" s="2" cm="1">
-        <f t="array" ref="D37">SUMPRODUCT((GROUP1!$D$2:$D$73=B37)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B37)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D37">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B37)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B37)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E37" s="2" cm="1">
-        <f t="array" ref="E37">SUMPRODUCT(((GROUP1!$D$2:$D$73=B37)+(GROUP1!$E$2:$E$73=B37))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E37">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B37)+('GROUP 1'!$E$2:$E$73=B37))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F37" s="2">
@@ -4581,11 +4610,11 @@
         <v>3</v>
       </c>
       <c r="G37" s="2">
-        <f>SUMIF(GROUP1!D:D,B37,GROUP1!F:F)+SUMIF(GROUP1!E:E,B37,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B37,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B37,'GROUP 1'!G:G)</f>
         <v>1</v>
       </c>
       <c r="H37" s="2">
-        <f>SUMIF(GROUP1!D:D,B37,GROUP1!G:G)+SUMIF(GROUP1!E:E,B37,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B37,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B37,'GROUP 1'!F:F)</f>
         <v>12</v>
       </c>
       <c r="I37" s="2">
@@ -4606,15 +4635,15 @@
         <v>76</v>
       </c>
       <c r="C38" s="2">
-        <f>COUNTIF(GROUP1!D:D,B38)+COUNTIF(GROUP1!E:E,B38)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B38)+COUNTIF('GROUP 1'!E:E,B38)</f>
         <v>3</v>
       </c>
       <c r="D38" s="2" cm="1">
-        <f t="array" ref="D38">SUMPRODUCT((GROUP1!$D$2:$D$73=B38)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B38)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D38">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B38)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B38)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>3</v>
       </c>
       <c r="E38" s="2" cm="1">
-        <f t="array" ref="E38">SUMPRODUCT(((GROUP1!$D$2:$D$73=B38)+(GROUP1!$E$2:$E$73=B38))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E38">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B38)+('GROUP 1'!$E$2:$E$73=B38))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F38" s="2">
@@ -4622,11 +4651,11 @@
         <v>0</v>
       </c>
       <c r="G38" s="2">
-        <f>SUMIF(GROUP1!D:D,B38,GROUP1!F:F)+SUMIF(GROUP1!E:E,B38,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B38,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B38,'GROUP 1'!G:G)</f>
         <v>8</v>
       </c>
       <c r="H38" s="2">
-        <f>SUMIF(GROUP1!D:D,B38,GROUP1!G:G)+SUMIF(GROUP1!E:E,B38,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B38,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B38,'GROUP 1'!F:F)</f>
         <v>1</v>
       </c>
       <c r="I38" s="2">
@@ -4647,15 +4676,15 @@
         <v>78</v>
       </c>
       <c r="C39" s="2">
-        <f>COUNTIF(GROUP1!D:D,B39)+COUNTIF(GROUP1!E:E,B39)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B39)+COUNTIF('GROUP 1'!E:E,B39)</f>
         <v>3</v>
       </c>
       <c r="D39" s="2" cm="1">
-        <f t="array" ref="D39">SUMPRODUCT((GROUP1!$D$2:$D$73=B39)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B39)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D39">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B39)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B39)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E39" s="2" cm="1">
-        <f t="array" ref="E39">SUMPRODUCT(((GROUP1!$D$2:$D$73=B39)+(GROUP1!$E$2:$E$73=B39))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E39">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B39)+('GROUP 1'!$E$2:$E$73=B39))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F39" s="2">
@@ -4663,11 +4692,11 @@
         <v>1</v>
       </c>
       <c r="G39" s="2">
-        <f>SUMIF(GROUP1!D:D,B39,GROUP1!F:F)+SUMIF(GROUP1!E:E,B39,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B39,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B39,'GROUP 1'!G:G)</f>
         <v>6</v>
       </c>
       <c r="H39" s="2">
-        <f>SUMIF(GROUP1!D:D,B39,GROUP1!G:G)+SUMIF(GROUP1!E:E,B39,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B39,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B39,'GROUP 1'!F:F)</f>
         <v>6</v>
       </c>
       <c r="I39" s="2">
@@ -4688,15 +4717,15 @@
         <v>77</v>
       </c>
       <c r="C40" s="2">
-        <f>COUNTIF(GROUP1!D:D,B40)+COUNTIF(GROUP1!E:E,B40)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B40)+COUNTIF('GROUP 1'!E:E,B40)</f>
         <v>3</v>
       </c>
       <c r="D40" s="2" cm="1">
-        <f t="array" ref="D40">SUMPRODUCT((GROUP1!$D$2:$D$73=B40)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B40)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D40">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B40)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B40)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E40" s="2" cm="1">
-        <f t="array" ref="E40">SUMPRODUCT(((GROUP1!$D$2:$D$73=B40)+(GROUP1!$E$2:$E$73=B40))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E40">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B40)+('GROUP 1'!$E$2:$E$73=B40))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F40" s="2">
@@ -4704,11 +4733,11 @@
         <v>1</v>
       </c>
       <c r="G40" s="2">
-        <f>SUMIF(GROUP1!D:D,B40,GROUP1!F:F)+SUMIF(GROUP1!E:E,B40,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B40,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B40,'GROUP 1'!G:G)</f>
         <v>5</v>
       </c>
       <c r="H40" s="2">
-        <f>SUMIF(GROUP1!D:D,B40,GROUP1!G:G)+SUMIF(GROUP1!E:E,B40,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B40,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B40,'GROUP 1'!F:F)</f>
         <v>7</v>
       </c>
       <c r="I40" s="2">
@@ -4729,15 +4758,15 @@
         <v>79</v>
       </c>
       <c r="C41" s="2">
-        <f>COUNTIF(GROUP1!D:D,B41)+COUNTIF(GROUP1!E:E,B41)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B41)+COUNTIF('GROUP 1'!E:E,B41)</f>
         <v>3</v>
       </c>
       <c r="D41" s="2" cm="1">
-        <f t="array" ref="D41">SUMPRODUCT((GROUP1!$D$2:$D$73=B41)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B41)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D41">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B41)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B41)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E41" s="2" cm="1">
-        <f t="array" ref="E41">SUMPRODUCT(((GROUP1!$D$2:$D$73=B41)+(GROUP1!$E$2:$E$73=B41))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E41">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B41)+('GROUP 1'!$E$2:$E$73=B41))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F41" s="2">
@@ -4745,11 +4774,11 @@
         <v>3</v>
       </c>
       <c r="G41" s="2">
-        <f>SUMIF(GROUP1!D:D,B41,GROUP1!F:F)+SUMIF(GROUP1!E:E,B41,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B41,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B41,'GROUP 1'!G:G)</f>
         <v>3</v>
       </c>
       <c r="H41" s="2">
-        <f>SUMIF(GROUP1!D:D,B41,GROUP1!G:G)+SUMIF(GROUP1!E:E,B41,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B41,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B41,'GROUP 1'!F:F)</f>
         <v>8</v>
       </c>
       <c r="I41" s="2">
@@ -4770,15 +4799,15 @@
         <v>85</v>
       </c>
       <c r="C42" s="2">
-        <f>COUNTIF(GROUP1!D:D,B42)+COUNTIF(GROUP1!E:E,B42)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B42)+COUNTIF('GROUP 1'!E:E,B42)</f>
         <v>3</v>
       </c>
       <c r="D42" s="2" cm="1">
-        <f t="array" ref="D42">SUMPRODUCT((GROUP1!$D$2:$D$73=B42)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B42)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D42">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B42)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B42)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E42" s="2" cm="1">
-        <f t="array" ref="E42">SUMPRODUCT(((GROUP1!$D$2:$D$73=B42)+(GROUP1!$E$2:$E$73=B42))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E42">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B42)+('GROUP 1'!$E$2:$E$73=B42))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F42" s="2">
@@ -4786,11 +4815,11 @@
         <v>0</v>
       </c>
       <c r="G42" s="2">
-        <f>SUMIF(GROUP1!D:D,B42,GROUP1!F:F)+SUMIF(GROUP1!E:E,B42,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B42,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B42,'GROUP 1'!G:G)</f>
         <v>4</v>
       </c>
       <c r="H42" s="2">
-        <f>SUMIF(GROUP1!D:D,B42,GROUP1!G:G)+SUMIF(GROUP1!E:E,B42,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B42,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B42,'GROUP 1'!F:F)</f>
         <v>1</v>
       </c>
       <c r="I42" s="2">
@@ -4811,15 +4840,15 @@
         <v>83</v>
       </c>
       <c r="C43" s="2">
-        <f>COUNTIF(GROUP1!D:D,B43)+COUNTIF(GROUP1!E:E,B43)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B43)+COUNTIF('GROUP 1'!E:E,B43)</f>
         <v>3</v>
       </c>
       <c r="D43" s="2" cm="1">
-        <f t="array" ref="D43">SUMPRODUCT((GROUP1!$D$2:$D$73=B43)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B43)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D43">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B43)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B43)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E43" s="2" cm="1">
-        <f t="array" ref="E43">SUMPRODUCT(((GROUP1!$D$2:$D$73=B43)+(GROUP1!$E$2:$E$73=B43))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E43">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B43)+('GROUP 1'!$E$2:$E$73=B43))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>2</v>
       </c>
       <c r="F43" s="2">
@@ -4827,11 +4856,11 @@
         <v>0</v>
       </c>
       <c r="G43" s="2">
-        <f>SUMIF(GROUP1!D:D,B43,GROUP1!F:F)+SUMIF(GROUP1!E:E,B43,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B43,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B43,'GROUP 1'!G:G)</f>
         <v>6</v>
       </c>
       <c r="H43" s="2">
-        <f>SUMIF(GROUP1!D:D,B43,GROUP1!G:G)+SUMIF(GROUP1!E:E,B43,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B43,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B43,'GROUP 1'!F:F)</f>
         <v>1</v>
       </c>
       <c r="I43" s="2">
@@ -4852,15 +4881,15 @@
         <v>84</v>
       </c>
       <c r="C44" s="2">
-        <f>COUNTIF(GROUP1!D:D,B44)+COUNTIF(GROUP1!E:E,B44)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B44)+COUNTIF('GROUP 1'!E:E,B44)</f>
         <v>3</v>
       </c>
       <c r="D44" s="2" cm="1">
-        <f t="array" ref="D44">SUMPRODUCT((GROUP1!$D$2:$D$73=B44)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B44)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D44">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B44)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B44)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E44" s="2" cm="1">
-        <f t="array" ref="E44">SUMPRODUCT(((GROUP1!$D$2:$D$73=B44)+(GROUP1!$E$2:$E$73=B44))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E44">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B44)+('GROUP 1'!$E$2:$E$73=B44))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F44" s="2">
@@ -4868,11 +4897,11 @@
         <v>1</v>
       </c>
       <c r="G44" s="2">
-        <f>SUMIF(GROUP1!D:D,B44,GROUP1!F:F)+SUMIF(GROUP1!E:E,B44,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B44,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B44,'GROUP 1'!G:G)</f>
         <v>4</v>
       </c>
       <c r="H44" s="2">
-        <f>SUMIF(GROUP1!D:D,B44,GROUP1!G:G)+SUMIF(GROUP1!E:E,B44,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B44,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B44,'GROUP 1'!F:F)</f>
         <v>3</v>
       </c>
       <c r="I44" s="2">
@@ -4893,15 +4922,15 @@
         <v>86</v>
       </c>
       <c r="C45" s="2">
-        <f>COUNTIF(GROUP1!D:D,B45)+COUNTIF(GROUP1!E:E,B45)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B45)+COUNTIF('GROUP 1'!E:E,B45)</f>
         <v>3</v>
       </c>
       <c r="D45" s="2" cm="1">
-        <f t="array" ref="D45">SUMPRODUCT((GROUP1!$D$2:$D$73=B45)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B45)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D45">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B45)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B45)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E45" s="2" cm="1">
-        <f t="array" ref="E45">SUMPRODUCT(((GROUP1!$D$2:$D$73=B45)+(GROUP1!$E$2:$E$73=B45))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E45">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B45)+('GROUP 1'!$E$2:$E$73=B45))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F45" s="2">
@@ -4909,11 +4938,11 @@
         <v>3</v>
       </c>
       <c r="G45" s="2">
-        <f>SUMIF(GROUP1!D:D,B45,GROUP1!F:F)+SUMIF(GROUP1!E:E,B45,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B45,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B45,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H45" s="2">
-        <f>SUMIF(GROUP1!D:D,B45,GROUP1!G:G)+SUMIF(GROUP1!E:E,B45,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B45,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B45,'GROUP 1'!F:F)</f>
         <v>11</v>
       </c>
       <c r="I45" s="2">
@@ -4934,15 +4963,15 @@
         <v>89</v>
       </c>
       <c r="C46" s="2">
-        <f>COUNTIF(GROUP1!D:D,B46)+COUNTIF(GROUP1!E:E,B46)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B46)+COUNTIF('GROUP 1'!E:E,B46)</f>
         <v>3</v>
       </c>
       <c r="D46" s="2" cm="1">
-        <f t="array" ref="D46">SUMPRODUCT((GROUP1!$D$2:$D$73=B46)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B46)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D46">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B46)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B46)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E46" s="2" cm="1">
-        <f t="array" ref="E46">SUMPRODUCT(((GROUP1!$D$2:$D$73=B46)+(GROUP1!$E$2:$E$73=B46))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E46">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B46)+('GROUP 1'!$E$2:$E$73=B46))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F46" s="2">
@@ -4950,11 +4979,11 @@
         <v>0</v>
       </c>
       <c r="G46" s="2">
-        <f>SUMIF(GROUP1!D:D,B46,GROUP1!F:F)+SUMIF(GROUP1!E:E,B46,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B46,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B46,'GROUP 1'!G:G)</f>
         <v>6</v>
       </c>
       <c r="H46" s="2">
-        <f>SUMIF(GROUP1!D:D,B46,GROUP1!G:G)+SUMIF(GROUP1!E:E,B46,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B46,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B46,'GROUP 1'!F:F)</f>
         <v>2</v>
       </c>
       <c r="I46" s="2">
@@ -4975,15 +5004,15 @@
         <v>90</v>
       </c>
       <c r="C47" s="2">
-        <f>COUNTIF(GROUP1!D:D,B47)+COUNTIF(GROUP1!E:E,B47)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B47)+COUNTIF('GROUP 1'!E:E,B47)</f>
         <v>3</v>
       </c>
       <c r="D47" s="2" cm="1">
-        <f t="array" ref="D47">SUMPRODUCT((GROUP1!$D$2:$D$73=B47)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B47)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D47">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B47)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B47)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>2</v>
       </c>
       <c r="E47" s="2" cm="1">
-        <f t="array" ref="E47">SUMPRODUCT(((GROUP1!$D$2:$D$73=B47)+(GROUP1!$E$2:$E$73=B47))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E47">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B47)+('GROUP 1'!$E$2:$E$73=B47))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F47" s="2">
@@ -4991,11 +5020,11 @@
         <v>1</v>
       </c>
       <c r="G47" s="2">
-        <f>SUMIF(GROUP1!D:D,B47,GROUP1!F:F)+SUMIF(GROUP1!E:E,B47,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B47,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B47,'GROUP 1'!G:G)</f>
         <v>5</v>
       </c>
       <c r="H47" s="2">
-        <f>SUMIF(GROUP1!D:D,B47,GROUP1!G:G)+SUMIF(GROUP1!E:E,B47,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B47,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B47,'GROUP 1'!F:F)</f>
         <v>5</v>
       </c>
       <c r="I47" s="2">
@@ -5016,15 +5045,15 @@
         <v>91</v>
       </c>
       <c r="C48" s="2">
-        <f>COUNTIF(GROUP1!D:D,B48)+COUNTIF(GROUP1!E:E,B48)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B48)+COUNTIF('GROUP 1'!E:E,B48)</f>
         <v>3</v>
       </c>
       <c r="D48" s="2" cm="1">
-        <f t="array" ref="D48">SUMPRODUCT((GROUP1!$D$2:$D$73=B48)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B48)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D48">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B48)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B48)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>1</v>
       </c>
       <c r="E48" s="2" cm="1">
-        <f t="array" ref="E48">SUMPRODUCT(((GROUP1!$D$2:$D$73=B48)+(GROUP1!$E$2:$E$73=B48))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E48">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B48)+('GROUP 1'!$E$2:$E$73=B48))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>1</v>
       </c>
       <c r="F48" s="2">
@@ -5032,11 +5061,11 @@
         <v>1</v>
       </c>
       <c r="G48" s="2">
-        <f>SUMIF(GROUP1!D:D,B48,GROUP1!F:F)+SUMIF(GROUP1!E:E,B48,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B48,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B48,'GROUP 1'!G:G)</f>
         <v>2</v>
       </c>
       <c r="H48" s="2">
-        <f>SUMIF(GROUP1!D:D,B48,GROUP1!G:G)+SUMIF(GROUP1!E:E,B48,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B48,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B48,'GROUP 1'!F:F)</f>
         <v>2</v>
       </c>
       <c r="I48" s="2">
@@ -5057,15 +5086,15 @@
         <v>92</v>
       </c>
       <c r="C49" s="2">
-        <f>COUNTIF(GROUP1!D:D,B49)+COUNTIF(GROUP1!E:E,B49)</f>
+        <f>COUNTIF('GROUP 1'!D:D,B49)+COUNTIF('GROUP 1'!E:E,B49)</f>
         <v>3</v>
       </c>
       <c r="D49" s="2" cm="1">
-        <f t="array" ref="D49">SUMPRODUCT((GROUP1!$D$2:$D$73=B49)*(GROUP1!$F$2:$F$73&gt;GROUP1!$G$2:$G$73))+SUMPRODUCT((GROUP1!$E$2:$E$73=B49)*(GROUP1!$G$2:$G$73&gt;GROUP1!$F$2:$F$73))</f>
+        <f t="array" ref="D49">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B49)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B49)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
         <v>0</v>
       </c>
       <c r="E49" s="2" cm="1">
-        <f t="array" ref="E49">SUMPRODUCT(((GROUP1!$D$2:$D$73=B49)+(GROUP1!$E$2:$E$73=B49))*(GROUP1!$F$2:$F$73=GROUP1!$G$2:$G$73))</f>
+        <f t="array" ref="E49">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B49)+('GROUP 1'!$E$2:$E$73=B49))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
         <v>0</v>
       </c>
       <c r="F49" s="2">
@@ -5073,11 +5102,11 @@
         <v>3</v>
       </c>
       <c r="G49" s="2">
-        <f>SUMIF(GROUP1!D:D,B49,GROUP1!F:F)+SUMIF(GROUP1!E:E,B49,GROUP1!G:G)</f>
+        <f>SUMIF('GROUP 1'!D:D,B49,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B49,'GROUP 1'!G:G)</f>
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <f>SUMIF(GROUP1!D:D,B49,GROUP1!G:G)+SUMIF(GROUP1!E:E,B49,GROUP1!F:F)</f>
+        <f>SUMIF('GROUP 1'!D:D,B49,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B49,'GROUP 1'!F:F)</f>
         <v>4</v>
       </c>
       <c r="I49" s="2">

--- a/FIFA.xlsx
+++ b/FIFA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analytics-portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25E730D9-4524-4C8C-9DF6-90B663A03DCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF1A2B8-7019-49B4-A06A-C4DDB96511E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" xr2:uid="{BB1EA6DA-86EB-4FC3-997E-079B42B60F51}"/>
+    <workbookView xWindow="12192" yWindow="0" windowWidth="12480" windowHeight="13200" xr2:uid="{BB1EA6DA-86EB-4FC3-997E-079B42B60F51}"/>
   </bookViews>
   <sheets>
     <sheet name="GROUP 1" sheetId="2" r:id="rId1"/>
@@ -1442,12 +1442,8 @@
       <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6">
-        <v>2</v>
-      </c>
-      <c r="G2" s="6">
-        <v>3</v>
-      </c>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
     </row>
     <row r="3" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6">
@@ -3172,27 +3168,27 @@
       </c>
       <c r="E2" s="2" cm="1">
         <f t="array" ref="E2">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B2)+('GROUP 1'!$E$2:$E$73=B2))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="2">
         <f>(C2-(D2+E2))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <f>SUMIF('GROUP 1'!D:D,B2,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B2,'GROUP 1'!G:G)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" s="2">
         <f>SUMIF('GROUP 1'!D:D,B2,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B2,'GROUP 1'!F:F)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <f>G2-H2</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" s="2">
         <f>D2*3+E2</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R2"/>
     </row>
@@ -3209,11 +3205,11 @@
       </c>
       <c r="D3" s="2" cm="1">
         <f t="array" ref="D3">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B3)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B3)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="2" cm="1">
         <f t="array" ref="E3">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B3)+('GROUP 1'!$E$2:$E$73=B3))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="2">
         <f t="shared" ref="F3:F49" si="0">(C3-(D3+E3))</f>
@@ -3221,19 +3217,19 @@
       </c>
       <c r="G3" s="2">
         <f>SUMIF('GROUP 1'!D:D,B3,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B3,'GROUP 1'!G:G)</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H3" s="2">
         <f>SUMIF('GROUP 1'!D:D,B3,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B3,'GROUP 1'!F:F)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I3" s="2">
         <f t="shared" ref="I3:I49" si="1">G3-H3</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J3" s="2">
         <f t="shared" ref="J3:J49" si="2">D3*3+E3</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R3"/>
     </row>

--- a/FIFA.xlsx
+++ b/FIFA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data-analytics-portfolio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF1A2B8-7019-49B4-A06A-C4DDB96511E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{182187A6-248E-486A-B207-2FBD23942AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12192" yWindow="0" windowWidth="12480" windowHeight="13200" xr2:uid="{BB1EA6DA-86EB-4FC3-997E-079B42B60F51}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="24792" windowHeight="13320" xr2:uid="{BB1EA6DA-86EB-4FC3-997E-079B42B60F51}"/>
   </bookViews>
   <sheets>
     <sheet name="GROUP 1" sheetId="2" r:id="rId1"/>
@@ -1442,8 +1442,12 @@
       <c r="E2" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
+      <c r="F2" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2" s="6">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:7" ht="31.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6">
@@ -3168,27 +3172,27 @@
       </c>
       <c r="E2" s="2" cm="1">
         <f t="array" ref="E2">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B2)+('GROUP 1'!$E$2:$E$73=B2))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
         <f>(C2-(D2+E2))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" s="2">
         <f>SUMIF('GROUP 1'!D:D,B2,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B2,'GROUP 1'!G:G)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" s="2">
         <f>SUMIF('GROUP 1'!D:D,B2,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B2,'GROUP 1'!F:F)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2">
         <f>G2-H2</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" s="2">
         <f>D2*3+E2</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R2"/>
     </row>
@@ -3205,11 +3209,11 @@
       </c>
       <c r="D3" s="2" cm="1">
         <f t="array" ref="D3">SUMPRODUCT(('GROUP 1'!$D$2:$D$73=B3)*('GROUP 1'!$F$2:$F$73&gt;'GROUP 1'!$G$2:$G$73))+SUMPRODUCT(('GROUP 1'!$E$2:$E$73=B3)*('GROUP 1'!$G$2:$G$73&gt;'GROUP 1'!$F$2:$F$73))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" cm="1">
         <f t="array" ref="E3">SUMPRODUCT((('GROUP 1'!$D$2:$D$73=B3)+('GROUP 1'!$E$2:$E$73=B3))*('GROUP 1'!$F$2:$F$73='GROUP 1'!$G$2:$G$73))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
         <f t="shared" ref="F3:F49" si="0">(C3-(D3+E3))</f>
@@ -3217,19 +3221,19 @@
       </c>
       <c r="G3" s="2">
         <f>SUMIF('GROUP 1'!D:D,B3,'GROUP 1'!F:F)+SUMIF('GROUP 1'!E:E,B3,'GROUP 1'!G:G)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H3" s="2">
         <f>SUMIF('GROUP 1'!D:D,B3,'GROUP 1'!G:G)+SUMIF('GROUP 1'!E:E,B3,'GROUP 1'!F:F)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I3" s="2">
         <f t="shared" ref="I3:I49" si="1">G3-H3</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="2">
         <f t="shared" ref="J3:J49" si="2">D3*3+E3</f>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R3"/>
     </row>
